--- a/sampleData/E2E Scenarios.xlsx
+++ b/sampleData/E2E Scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/AZOnline_Automation/AZOnline/sampleData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D49D6FC-F02B-6B4D-827F-B75B1AD10C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0E13E1-049B-9B45-8775-47D5DDDB0FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="-18980" windowWidth="28040" windowHeight="17180" xr2:uid="{D83822C5-8D5C-BA46-87AE-E8A3864EF61D}"/>
+    <workbookView xWindow="4700" yWindow="2040" windowWidth="28040" windowHeight="17180" xr2:uid="{D83822C5-8D5C-BA46-87AE-E8A3864EF61D}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenarios" sheetId="1" r:id="rId1"/>
@@ -62,57 +62,6 @@
     <t>Execute</t>
   </si>
   <si>
-    <t>TotalSteps</t>
-  </si>
-  <si>
-    <t>Step1Action</t>
-  </si>
-  <si>
-    <t>Step1SubType</t>
-  </si>
-  <si>
-    <t>Step1Portal</t>
-  </si>
-  <si>
-    <t>Step1TestCaseId</t>
-  </si>
-  <si>
-    <t>Step2Action</t>
-  </si>
-  <si>
-    <t>Step2SubType</t>
-  </si>
-  <si>
-    <t>Step2Portal</t>
-  </si>
-  <si>
-    <t>Step2TestCaseId</t>
-  </si>
-  <si>
-    <t>Step3Action</t>
-  </si>
-  <si>
-    <t>Step3SubType</t>
-  </si>
-  <si>
-    <t>Step3Portal</t>
-  </si>
-  <si>
-    <t>Step3TestCaseId</t>
-  </si>
-  <si>
-    <t>Step4Action</t>
-  </si>
-  <si>
-    <t>Step4SubType</t>
-  </si>
-  <si>
-    <t>Step4Portal</t>
-  </si>
-  <si>
-    <t>Step4TestCaseId</t>
-  </si>
-  <si>
     <t>SC001</t>
   </si>
   <si>
@@ -327,6 +276,57 @@
   </si>
   <si>
     <t>MTA_RC_05</t>
+  </si>
+  <si>
+    <t>TotalItems</t>
+  </si>
+  <si>
+    <t>Item1Action</t>
+  </si>
+  <si>
+    <t>Item1SubType</t>
+  </si>
+  <si>
+    <t>Item1Portal</t>
+  </si>
+  <si>
+    <t>Item1TestCaseId</t>
+  </si>
+  <si>
+    <t>Item2Action</t>
+  </si>
+  <si>
+    <t>Item2SubType</t>
+  </si>
+  <si>
+    <t>Item2Portal</t>
+  </si>
+  <si>
+    <t>Item2TestCaseId</t>
+  </si>
+  <si>
+    <t>Item3Action</t>
+  </si>
+  <si>
+    <t>Item3SubType</t>
+  </si>
+  <si>
+    <t>Item3Portal</t>
+  </si>
+  <si>
+    <t>Item3TestCaseId</t>
+  </si>
+  <si>
+    <t>Item4Action</t>
+  </si>
+  <si>
+    <t>Item4SubType</t>
+  </si>
+  <si>
+    <t>Item4Portal</t>
+  </si>
+  <si>
+    <t>Item4TestCaseId</t>
   </si>
 </sst>
 </file>
@@ -738,10 +738,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -759,528 +759,528 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="L1" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="M1" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="N1" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="O1" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="P1" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="Q1" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="R1" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="S1" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="T1" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="U1" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="V1" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="W1" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="X1" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="Y1" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="Z1" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="AA1" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K3">
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="S3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K4">
         <v>3</v>
       </c>
       <c r="L4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
+        <v>13</v>
+      </c>
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" t="s">
+        <v>26</v>
+      </c>
+      <c r="U4" t="s">
         <v>27</v>
       </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>41</v>
-      </c>
-      <c r="R4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s">
-        <v>42</v>
-      </c>
-      <c r="T4" t="s">
-        <v>43</v>
-      </c>
-      <c r="U4" t="s">
-        <v>44</v>
-      </c>
       <c r="V4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="W4" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G5" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="M5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O5" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K6">
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="M6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" t="s">
         <v>41</v>
       </c>
-      <c r="N6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" t="s">
-        <v>58</v>
-      </c>
       <c r="P6" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="R6" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="S6" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="O7" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K8">
         <v>4</v>
       </c>
       <c r="L8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O8" t="s">
+        <v>52</v>
+      </c>
+      <c r="P8" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>19</v>
+      </c>
+      <c r="R8" t="s">
+        <v>13</v>
+      </c>
+      <c r="S8" t="s">
+        <v>53</v>
+      </c>
+      <c r="T8" t="s">
+        <v>18</v>
+      </c>
+      <c r="U8" t="s">
+        <v>54</v>
+      </c>
+      <c r="V8" t="s">
+        <v>13</v>
+      </c>
+      <c r="W8" t="s">
+        <v>55</v>
+      </c>
+      <c r="X8" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y8" t="s">
         <v>27</v>
       </c>
-      <c r="N8" t="s">
-        <v>30</v>
-      </c>
-      <c r="O8" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>36</v>
-      </c>
-      <c r="R8" t="s">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s">
-        <v>70</v>
-      </c>
-      <c r="T8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U8" t="s">
-        <v>71</v>
-      </c>
-      <c r="V8" t="s">
-        <v>30</v>
-      </c>
-      <c r="W8" t="s">
-        <v>72</v>
-      </c>
-      <c r="X8" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>44</v>
-      </c>
       <c r="Z8" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O9" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="J11" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="K11">
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N11" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="P11" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="Q11" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="S11" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/sampleData/E2E Scenarios.xlsx
+++ b/sampleData/E2E Scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vijaytomar/AZOnline_Automation/AZOnline/sampleData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0E13E1-049B-9B45-8775-47D5DDDB0FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4767420-4544-D942-A1E5-3E039C76B13F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4700" yWindow="2040" windowWidth="28040" windowHeight="17180" xr2:uid="{D83822C5-8D5C-BA46-87AE-E8A3864EF61D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="100">
   <si>
     <t>ScenarioId</t>
   </si>
@@ -44,9 +44,6 @@
     <t>ScenarioName</t>
   </si>
   <si>
-    <t>Journey</t>
-  </si>
-  <si>
     <t>PolicyNumber</t>
   </si>
   <si>
@@ -65,9 +62,6 @@
     <t>SC001</t>
   </si>
   <si>
-    <t>Direct</t>
-  </si>
-  <si>
     <t>NewBusiness</t>
   </si>
   <si>
@@ -209,12 +203,6 @@
     <t>REN_STD_03</t>
   </si>
   <si>
-    <t>PolicyContext</t>
-  </si>
-  <si>
-    <t>EntryPoint</t>
-  </si>
-  <si>
     <t>New Business Only (Direct)</t>
   </si>
   <si>
@@ -290,9 +278,6 @@
     <t>Item1Portal</t>
   </si>
   <si>
-    <t>Item1TestCaseId</t>
-  </si>
-  <si>
     <t>Item2Action</t>
   </si>
   <si>
@@ -302,9 +287,6 @@
     <t>Item2Portal</t>
   </si>
   <si>
-    <t>Item2TestCaseId</t>
-  </si>
-  <si>
     <t>Item3Action</t>
   </si>
   <si>
@@ -314,9 +296,6 @@
     <t>Item3Portal</t>
   </si>
   <si>
-    <t>Item3TestCaseId</t>
-  </si>
-  <si>
     <t>Item4Action</t>
   </si>
   <si>
@@ -326,7 +305,37 @@
     <t>Item4Portal</t>
   </si>
   <si>
-    <t>Item4TestCaseId</t>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Item1TestCaseRef</t>
+  </si>
+  <si>
+    <t>Item2TestCaseRef</t>
+  </si>
+  <si>
+    <t>Item3TestCaseRef</t>
+  </si>
+  <si>
+    <t>Item4TestCaseRef</t>
+  </si>
+  <si>
+    <t>Athena</t>
+  </si>
+  <si>
+    <t>AzOnline</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>JourneyStartWith</t>
   </si>
 </sst>
 </file>
@@ -698,12 +707,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8162A46C-1970-C343-9849-E064686BC197}">
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
@@ -727,7 +736,7 @@
     <col min="26" max="26" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,552 +744,594 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" t="s">
+        <v>93</v>
+      </c>
+      <c r="U1" t="s">
+        <v>83</v>
+      </c>
+      <c r="V1" t="s">
+        <v>84</v>
+      </c>
+      <c r="W1" t="s">
+        <v>85</v>
+      </c>
+      <c r="X1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" t="s">
+        <v>11</v>
+      </c>
+      <c r="T3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
+        <v>11</v>
+      </c>
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O6" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>40</v>
+      </c>
+      <c r="R6" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" t="s">
+        <v>26</v>
+      </c>
+      <c r="T6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="C8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M1" t="s">
-        <v>82</v>
-      </c>
-      <c r="N1" t="s">
-        <v>83</v>
-      </c>
-      <c r="O1" t="s">
-        <v>84</v>
-      </c>
-      <c r="P1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>86</v>
-      </c>
-      <c r="R1" t="s">
-        <v>87</v>
-      </c>
-      <c r="S1" t="s">
-        <v>88</v>
-      </c>
-      <c r="T1" t="s">
-        <v>89</v>
-      </c>
-      <c r="U1" t="s">
-        <v>90</v>
-      </c>
-      <c r="V1" t="s">
-        <v>91</v>
-      </c>
-      <c r="W1" t="s">
-        <v>92</v>
-      </c>
-      <c r="X1" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>96</v>
+      <c r="M8" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" t="s">
+        <v>11</v>
+      </c>
+      <c r="P8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S8" t="s">
+        <v>11</v>
+      </c>
+      <c r="T8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U8" t="s">
+        <v>16</v>
+      </c>
+      <c r="V8" t="s">
+        <v>52</v>
+      </c>
+      <c r="W8" t="s">
+        <v>11</v>
+      </c>
+      <c r="X8" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" t="s">
         <v>11</v>
       </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2">
+      <c r="P9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M10" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" t="s">
+        <v>11</v>
+      </c>
+      <c r="P10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" t="s">
         <v>10</v>
       </c>
-      <c r="N2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" t="s">
+        <v>11</v>
+      </c>
+      <c r="P11" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q11" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3">
-        <v>2</v>
-      </c>
-      <c r="L3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" t="s">
-        <v>13</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="R11" t="s">
         <v>17</v>
       </c>
-      <c r="P3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R3" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" t="s">
-        <v>13</v>
-      </c>
-      <c r="S4" t="s">
-        <v>25</v>
-      </c>
-      <c r="T4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V4" t="s">
-        <v>28</v>
-      </c>
-      <c r="W4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" t="s">
-        <v>13</v>
-      </c>
-      <c r="O5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-      <c r="L6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" t="s">
-        <v>13</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>43</v>
-      </c>
-      <c r="R6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
-      </c>
-      <c r="L8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" t="s">
-        <v>13</v>
-      </c>
-      <c r="O8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>19</v>
-      </c>
-      <c r="R8" t="s">
-        <v>13</v>
-      </c>
-      <c r="S8" t="s">
-        <v>53</v>
-      </c>
-      <c r="T8" t="s">
-        <v>18</v>
-      </c>
-      <c r="U8" t="s">
-        <v>54</v>
-      </c>
-      <c r="V8" t="s">
-        <v>13</v>
-      </c>
-      <c r="W8" t="s">
-        <v>55</v>
-      </c>
-      <c r="X8" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>10</v>
-      </c>
-      <c r="N9" t="s">
-        <v>13</v>
-      </c>
-      <c r="O9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" t="s">
-        <v>72</v>
-      </c>
-      <c r="J10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" t="s">
-        <v>13</v>
-      </c>
-      <c r="O10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="S11" t="s">
+        <v>11</v>
+      </c>
+      <c r="T11" t="s">
         <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" t="s">
-        <v>77</v>
-      </c>
-      <c r="J11" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11" t="s">
-        <v>10</v>
-      </c>
-      <c r="N11" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" t="s">
-        <v>78</v>
-      </c>
-      <c r="P11" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>19</v>
-      </c>
-      <c r="R11" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
